--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0001T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0001T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.01381963049528</v>
+        <v>7.802245689955483</v>
       </c>
       <c r="D2" t="n">
-        <v>46.39836081045736</v>
+        <v>7.539733631699321</v>
       </c>
       <c r="E2" t="n">
-        <v>12.55808079332965</v>
+        <v>2.040688128916068</v>
       </c>
       <c r="F2" t="n">
-        <v>6.189289511242283</v>
+        <v>1.005759545576871</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>78.5031574141593</v>
+        <v>12.75676307980089</v>
       </c>
       <c r="D3" t="n">
-        <v>45.90897467540595</v>
+        <v>7.460208384753467</v>
       </c>
       <c r="E3" t="n">
-        <v>12.55808079332965</v>
+        <v>2.040688128916068</v>
       </c>
       <c r="F3" t="n">
-        <v>6.189289511242283</v>
+        <v>1.005759545576871</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.72656545007538</v>
+        <v>9.70556688563725</v>
       </c>
       <c r="D4" t="n">
-        <v>59.27629121733632</v>
+        <v>9.632397322817152</v>
       </c>
       <c r="E4" t="n">
-        <v>12.55808079332965</v>
+        <v>2.040688128916068</v>
       </c>
       <c r="F4" t="n">
-        <v>6.189289511242283</v>
+        <v>1.005759545576871</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
